--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_rf_dose_att.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_rf_dose_att.xlsx
@@ -488,10 +488,10 @@
         <v>-0.0245978163235562</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.014406710899961</v>
+        <v>0.0341412602485213</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>-0.0189852442972044</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.0131778244356288</v>
+        <v>0.0298992740799261</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>-0.0109396111596074</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0113589627355306</v>
+        <v>0.0231722419212086</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>-0.00626292169287287</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0102669562227676</v>
+        <v>0.0212213235789502</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>0.00276372420696379</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.00807543230458232</v>
+        <v>0.0194440820024604</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>0.00680745167577247</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.0076896765433937</v>
+        <v>0.0191163852583438</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>0.00870139479195347</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.00793058014602204</v>
+        <v>0.0185439147616577</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>0.0108221130979231</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.00817878245572858</v>
+        <v>0.0177124281982657</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>0.0124988700194817</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.00835812129493549</v>
+        <v>0.0167127475354468</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>0.0165648384986161</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.00872287273751102</v>
+        <v>0.0168303489528356</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>0.0193086264764585</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.00715448868162294</v>
+        <v>0.0159782894566805</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>0.0233255864266219</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.00489496591698197</v>
+        <v>0.0157547946241062</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>0.0257617388764933</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.00354816564055568</v>
+        <v>0.0164150008091462</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>0.0270940445630911</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.00281985381886035</v>
+        <v>0.0169801372504974</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>0.0293387872530788</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.00160696445814176</v>
+        <v>0.0183630583733688</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>0.034720054128186</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.00121861842139798</v>
+        <v>0.018608401613476</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>0.0364125066735716</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.00207994589474943</v>
+        <v>0.0193367749032079</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>0.0387871034503075</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.00326296602830846</v>
+        <v>0.0204791522419877</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>0.0410138618072763</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.00434233070195245</v>
+        <v>0.0210980071156075</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>0.0427312571018898</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.00515263624111226</v>
+        <v>0.0206740629750469</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>0.0447907523637677</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.00609588440206356</v>
+        <v>0.0203771319263049</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>0.0465227205525571</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.00686231199154189</v>
+        <v>0.0201014680368711</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>0.048746519597175</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.00780557966622456</v>
+        <v>0.0195617092333253</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>0.0514306583205142</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.00887293767167068</v>
+        <v>0.0197391313111051</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>0.0520649032596918</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.00911214967122169</v>
+        <v>0.0195452787662128</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>0.0549322426002858</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.0101205863818554</v>
+        <v>0.0188542460968444</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>0.055610549547646</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.0103394730387805</v>
+        <v>0.0184647652155506</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>0.0562715642041833</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.0105445976483104</v>
+        <v>0.0181167321750191</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>0.0580126752840475</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.0110423063594324</v>
+        <v>0.0184043514572172</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>0.0589787096951067</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.0112887416500111</v>
+        <v>0.0188623363714748</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>0.0597131739969512</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.0116525593448723</v>
+        <v>0.0190029716874676</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>0.0615807374275395</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.0126050414325124</v>
+        <v>0.0192272916042402</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>0.0624127456848764</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.0124485791753251</v>
+        <v>0.0188368999748157</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>0.0636973587717994</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.012156369998311</v>
+        <v>0.0185780361814058</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>0.0645989663009847</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.0119126611149659</v>
+        <v>0.0174015716799431</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>0.0651352455867198</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.0117521605575639</v>
+        <v>0.0166744649840522</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>0.0659477379929471</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.0114869096005232</v>
+        <v>0.0172150579849176</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>0.0689613600369519</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.0103043587650624</v>
+        <v>0.0167754394504384</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>0.0695000951556127</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.0100742449798021</v>
+        <v>0.0167132554187708</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>0.0698228432924121</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.00993697821760099</v>
+        <v>0.0168037091955778</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>0.071687186254382</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.0096202561992537</v>
+        <v>0.0185108076877228</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>0.072406861506325</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.010456661983909</v>
+        <v>0.0196555007953323</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>0.0729468012834639</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.011076737369666</v>
+        <v>0.0196955419058526</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>0.0744606538475004</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.0123542922747243</v>
+        <v>0.0188838735249911</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>0.0748149315446096</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.0124368571068987</v>
+        <v>0.0184884872171834</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>0.0763405737198956</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.0126799947339542</v>
+        <v>0.019269746966156</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>0.0765885606506918</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.0127025848189927</v>
+        <v>0.0194549052340083</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>0.0775814829710769</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.0127468639898786</v>
+        <v>0.0209734771888197</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>0.0777696038144744</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.01274705703102</v>
+        <v>0.0213011635954737</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>0.0783678997539797</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.0127306763413289</v>
+        <v>0.0230301537599249</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>0.0791802958932533</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.012667892618012</v>
+        <v>0.0229076379432148</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>0.0805908105098998</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.0124524185586177</v>
+        <v>0.0232357461898316</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>0.0810374214092345</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.0123572313372539</v>
+        <v>0.0232923518414963</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>0.0828791268821069</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.0118369774966882</v>
+        <v>0.0242056717719753</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>0.0834643027417677</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.0116312487237473</v>
+        <v>0.0244741296948545</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>0.0842822234486793</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.0117618796633018</v>
+        <v>0.0242775068818019</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>0.0854534273741349</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.0120576921805242</v>
+        <v>0.0249011087757717</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>0.0867336367202498</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.0122466311169429</v>
+        <v>0.025521588382529</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>0.0878158381650609</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.0123011746430896</v>
+        <v>0.0249900000921611</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>0.0885631367665233</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.0122848134436105</v>
+        <v>0.0250030305141403</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>0.0893323046381319</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.0122235693696012</v>
+        <v>0.0243994556589115</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>0.0896264695012831</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.0121885679391791</v>
+        <v>0.0241413128617507</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>0.0899583528951135</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>0.0121415601544173</v>
+        <v>0.0238378449226103</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>0.0901496317436702</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>0.0121108961542628</v>
+        <v>0.0236571702632951</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>0.0932987676835872</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>0.0112549691448594</v>
+        <v>0.0251302383087948</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>0.0941818659000229</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>0.0109058798393978</v>
+        <v>0.0238151675898963</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>0.0950944558415</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>0.010500334877906</v>
+        <v>0.0236109697863632</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>0.0963674745976016</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>0.00986431929032825</v>
+        <v>0.0232402000844608</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>0.0970326303002023</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>0.00950190190548014</v>
+        <v>0.0227045995041955</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>0.0979106931185025</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>0.00899439766012299</v>
+        <v>0.0231647978768683</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>0.0985337292175703</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>0.0086155622433336</v>
+        <v>0.0238075415418576</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>0.0997294025788751</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>0.00784880105404122</v>
+        <v>0.0232608519844371</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>0.100874188102435</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>0.00707077097536156</v>
+        <v>0.0225126128667766</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>0.104586819415437</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>0.00505911065828994</v>
+        <v>0.0219125861215916</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>0.105878428410351</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>0.00464180158089871</v>
+        <v>0.0217826573032448</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>0.108968855785686</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>0.0033202469211049</v>
+        <v>0.0217013293495515</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>0.113169926564908</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>0.00349384545665441</v>
+        <v>0.0237290571571329</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>0.115149317323418</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>0.00426289317824038</v>
+        <v>0.0245503566808064</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>0.118919746951634</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>0.00722490944195626</v>
+        <v>0.0271140937916651</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>0.125539175956349</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>0.00960123164404989</v>
+        <v>0.0293931554025424</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>0.127550925726375</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>0.0100838378875359</v>
+        <v>0.0305983988209758</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>0.130577375932174</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>0.0120664488972429</v>
+        <v>0.03218541285522</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>0.13645238995804</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.0183961636789682</v>
+        <v>0.0389039348021731</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>0.14046703105901</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>0.0236329187980833</v>
+        <v>0.0392337527697064</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>0.148396956852682</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>0.0359494285482465</v>
+        <v>0.0441055913269277</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>0.155508852380927</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>0.0468862712965198</v>
+        <v>0.0464103156740438</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>0.165514170385315</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>0.0479945395433809</v>
+        <v>0.0531302665198819</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>0.183879147732613</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>0.0385567691558972</v>
+        <v>0.0666623510239665</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>0.205854840882724</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>0.0210922928743321</v>
+        <v>0.0946296787888824</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>0.243699904859678</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>0.0279715090966293</v>
+        <v>0.158128679201662</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>21.2366096039472</v>
+        <v>2.68848579490179</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
